--- a/data/growing_cons_network.xlsx
+++ b/data/growing_cons_network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MONASH_UNI\_Y3S1\FIT3179\DV2_repo\FIT3179_DV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AF2F32-C2A1-4A3D-9A0F-4109AF7DAE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A3674A-AE1D-4007-9A32-ACBD1A8E7386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
